--- a/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>ALIZY</t>
   </si>
@@ -656,58 +656,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -735,8 +738,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -764,8 +770,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,8 +802,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -806,8 +818,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -835,8 +848,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -864,8 +880,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -893,8 +912,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -922,8 +944,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -932,8 +957,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -961,8 +987,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -990,8 +1019,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1003,8 +1035,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1032,8 +1065,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1061,8 +1097,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1090,8 +1129,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1119,8 +1161,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1148,8 +1193,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1177,8 +1225,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1206,8 +1257,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1235,8 +1289,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1264,8 +1321,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1293,8 +1353,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1322,8 +1385,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1351,8 +1417,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1380,8 +1449,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1409,8 +1481,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1438,8 +1513,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1467,42 +1545,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1514,8 +1598,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1527,95 +1612,105 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22605900</v>
+      </c>
+      <c r="E41" s="3">
         <v>34527100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>30063200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30605200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20913000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25551400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27960700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26655800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18939800</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>112638000</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>104819500</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>104830300</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>106995700</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>90836200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>86247700</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13350200</v>
+      </c>
+      <c r="E43" s="3">
         <v>121600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15825600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>83100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14954100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>175700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14693200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>385700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13139900</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1643,153 +1738,171 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80983500</v>
+      </c>
+      <c r="E45" s="3">
         <v>30363600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>47159500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>27186300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45268000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26119800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>45360300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27195800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40840000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>233389600</v>
+      </c>
+      <c r="E46" s="3">
         <v>65012300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>197867800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>57874600</v>
       </c>
-      <c r="G46" s="3">
-        <v>189767900</v>
-      </c>
       <c r="H46" s="3">
+        <v>191933200</v>
+      </c>
+      <c r="I46" s="3">
         <v>51847000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>180161600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>54237300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>162741300</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>551799400</v>
+      </c>
+      <c r="E47" s="3">
         <v>827557400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>551094000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>793370400</v>
       </c>
-      <c r="G47" s="3">
-        <v>570855500</v>
-      </c>
       <c r="H47" s="3">
+        <v>570507400</v>
+      </c>
+      <c r="I47" s="3">
         <v>733580700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>551375500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>764370900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>539297900</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3">
+        <v>6789500</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>7192800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3">
-        <v>11292100</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
+        <v>7431200</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>7437800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>11064400</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23647400</v>
+      </c>
+      <c r="E49" s="3">
         <v>21017200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24098400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20502800</v>
       </c>
-      <c r="G49" s="3">
-        <v>20613500</v>
-      </c>
       <c r="H49" s="3">
+        <v>24474400</v>
+      </c>
+      <c r="I49" s="3">
         <v>19753400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24162700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20309600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19709300</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1817,8 +1930,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1846,37 +1962,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>182559300</v>
+      </c>
+      <c r="E52" s="3">
         <v>223850100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>204814100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>204572200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>203300500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>186259500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>196905000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>194128600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>185163000</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1904,37 +2026,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1081455600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1144868400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1069703200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1082890300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1086740400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>997746600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1045554600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1039247100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1000210500</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1946,8 +2074,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1959,182 +2088,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>327200</v>
+      </c>
+      <c r="E57" s="3">
         <v>294400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>286100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>352800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>255300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>286800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1117900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>384600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1949500</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>1169000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>1219200</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1728700</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1149600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1200200</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>52414300</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>22747200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
-        <v>16154500</v>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H59" s="3">
+        <v>18754300</v>
+      </c>
+      <c r="I59" s="3">
         <v>57094600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16325300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>57856400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11474800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61825200</v>
+      </c>
+      <c r="E60" s="3">
         <v>294400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32075400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>352800</v>
       </c>
-      <c r="G60" s="3">
-        <v>24621400</v>
-      </c>
       <c r="H60" s="3">
+        <v>27766100</v>
+      </c>
+      <c r="I60" s="3">
         <v>57381500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25042600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>58241000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19373700</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>34167100</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>32788000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
-        <v>34992800</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>34482100</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>32381000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>33253200</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>907479000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1073335900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>930779000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1011798500</v>
       </c>
-      <c r="G62" s="3">
-        <v>944176000</v>
-      </c>
       <c r="H62" s="3">
+        <v>943774700</v>
+      </c>
+      <c r="I62" s="3">
         <v>873972300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>912053500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>912163200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>873310900</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2162,8 +2310,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2191,8 +2342,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2220,37 +2374,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1015117500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1076413100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1006690200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1014468700</v>
       </c>
-      <c r="G66" s="3">
-        <v>1016462900</v>
-      </c>
       <c r="H66" s="3">
+        <v>1018695700</v>
+      </c>
+      <c r="I66" s="3">
         <v>933511900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>981336200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>972554300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>937439400</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2262,8 +2422,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2291,8 +2452,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2320,8 +2484,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2349,8 +2516,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2378,37 +2548,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34493200</v>
+      </c>
+      <c r="E72" s="3">
         <v>34462400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31150800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>35260500</v>
       </c>
-      <c r="G72" s="3">
-        <v>33936100</v>
-      </c>
       <c r="H72" s="3">
+        <v>33673000</v>
+      </c>
+      <c r="I72" s="3">
         <v>31308200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30490200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>31371200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2436,8 +2612,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2465,8 +2644,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2494,37 +2676,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62415400</v>
+      </c>
+      <c r="E76" s="3">
         <v>64434500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>59478200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64709200</v>
       </c>
-      <c r="G76" s="3">
-        <v>64636900</v>
-      </c>
       <c r="H76" s="3">
+        <v>64373800</v>
+      </c>
+      <c r="I76" s="3">
         <v>59366000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59299100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>61679700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58154300</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2552,42 +2740,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2615,8 +2809,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2628,8 +2825,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2657,8 +2855,11 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2686,8 +2887,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2715,8 +2919,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2744,8 +2951,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2773,8 +2983,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2802,8 +3015,11 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -2831,8 +3047,11 @@
       <c r="K89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2844,8 +3063,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2873,8 +3093,11 @@
       <c r="K91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2902,8 +3125,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2931,8 +3157,11 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -2960,8 +3189,11 @@
       <c r="K94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2973,8 +3205,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3002,8 +3235,11 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3031,8 +3267,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3060,8 +3299,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3089,8 +3331,11 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3118,8 +3363,11 @@
       <c r="K100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3147,8 +3395,11 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3174,6 +3425,9 @@
         <v>4</v>
       </c>
       <c r="K102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="92">
   <si>
     <t>ALIZY</t>
   </si>
@@ -656,61 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -741,8 +753,14 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -773,8 +791,14 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -805,8 +829,14 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -819,8 +849,10 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -851,8 +883,14 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -883,8 +921,14 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -915,8 +959,14 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -947,8 +997,14 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -958,8 +1014,10 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -990,8 +1048,14 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1022,8 +1086,14 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1036,8 +1106,10 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1068,8 +1140,14 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1100,8 +1178,14 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1132,8 +1216,14 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1164,8 +1254,14 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1196,8 +1292,14 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1228,8 +1330,14 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1260,8 +1368,14 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1292,8 +1406,14 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1324,8 +1444,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1356,8 +1482,14 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1388,8 +1520,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1420,8 +1558,14 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1452,8 +1596,14 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1484,8 +1634,14 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1516,8 +1672,14 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1548,45 +1710,57 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1599,8 +1773,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1613,104 +1789,124 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39795700</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41" s="3">
         <v>22605900</v>
       </c>
-      <c r="E41" s="3">
-        <v>34527100</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
         <v>30063200</v>
       </c>
-      <c r="G41" s="3">
-        <v>30605200</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3">
         <v>20913000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>25551400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>27960700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>26655800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18939800</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>115418700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>112638000</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>104819500</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>106995700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>90836200</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>86247700</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16662400</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>13350200</v>
       </c>
-      <c r="E43" s="3">
-        <v>121600</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>15825600</v>
       </c>
-      <c r="G43" s="3">
-        <v>83100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3">
         <v>14954100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>175700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14693200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>385700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>13139900</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1741,168 +1937,204 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55913100</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3">
         <v>80983500</v>
       </c>
-      <c r="E45" s="3">
-        <v>30363600</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>47159500</v>
       </c>
-      <c r="G45" s="3">
-        <v>27186300</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>45268000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>26119800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>45360300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27195800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>40840000</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>229107500</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3">
         <v>233389600</v>
       </c>
-      <c r="E46" s="3">
-        <v>65012300</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>197867800</v>
       </c>
-      <c r="G46" s="3">
-        <v>57874600</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3">
         <v>191933200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>51847000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>180161600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>54237300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>162741300</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>608482700</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>551799400</v>
       </c>
-      <c r="E47" s="3">
-        <v>827557400</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>551094000</v>
       </c>
-      <c r="G47" s="3">
-        <v>793370400</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3">
         <v>570507400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>733580700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>551375500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>764370900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>539297900</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7421000</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>6789500</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>7192800</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3">
         <v>7431200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>7437800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>11064400</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25903700</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3">
         <v>23647400</v>
       </c>
-      <c r="E49" s="3">
-        <v>21017200</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
         <v>24098400</v>
       </c>
-      <c r="G49" s="3">
-        <v>20502800</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3">
         <v>24474400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>19753400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>24162700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20309600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>19709300</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1933,8 +2165,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1965,40 +2203,52 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205978900</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3">
         <v>182559300</v>
       </c>
-      <c r="E52" s="3">
-        <v>223850100</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>204814100</v>
       </c>
-      <c r="G52" s="3">
-        <v>204572200</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3">
         <v>203300500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>186259500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>196905000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>194128600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>185163000</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2029,40 +2279,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1166041100</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3">
         <v>1081455600</v>
       </c>
-      <c r="E54" s="3">
-        <v>1144868400</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>1069703200</v>
       </c>
-      <c r="G54" s="3">
-        <v>1082890300</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3">
         <v>1086740400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>997746600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1045554600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1039247100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1000210500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2075,8 +2337,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2089,200 +2353,238 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>327200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>294400</v>
+        <v>110378200</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F57" s="3">
-        <v>286100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>352800</v>
+        <v>97721300</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H57" s="3">
-        <v>255300</v>
-      </c>
-      <c r="I57" s="3">
+        <v>96351700</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3">
+        <v>97379200</v>
+      </c>
+      <c r="K57" s="3">
         <v>286800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1117900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>384600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1949500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>1448000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F58" s="3">
+        <v>2442300</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>1169000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
         <v>1728700</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>1149600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1200200</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20689400</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3">
         <v>52414300</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>22747200</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
         <v>18754300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>57094600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>16325300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>57856400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>11474800</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>61825200</v>
-      </c>
-      <c r="E60" s="3">
-        <v>294400</v>
+        <v>140779800</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F60" s="3">
-        <v>32075400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>352800</v>
+        <v>159712200</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H60" s="3">
-        <v>27766100</v>
-      </c>
-      <c r="I60" s="3">
+        <v>128141000</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3">
+        <v>124890000</v>
+      </c>
+      <c r="K60" s="3">
         <v>57381500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>25042600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>58241000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19373700</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>34167100</v>
+        <v>41866100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>33625600</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>32788000</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>34482100</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>34430200</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>32381000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>33253200</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>907479000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1073335900</v>
+        <v>899492700</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
-        <v>930779000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1011798500</v>
+        <v>810133600</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H62" s="3">
-        <v>943774700</v>
-      </c>
-      <c r="I62" s="3">
+        <v>834713400</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3">
+        <v>846702800</v>
+      </c>
+      <c r="K62" s="3">
         <v>873972300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>912053500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>912163200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>873310900</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2313,8 +2615,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2345,8 +2653,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2377,40 +2691,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1094975900</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3">
         <v>1015117500</v>
       </c>
-      <c r="E66" s="3">
-        <v>1076413100</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>1006690200</v>
       </c>
-      <c r="G66" s="3">
-        <v>1014468700</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3">
         <v>1018695700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>933511900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>981336200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>972554300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>937439400</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2423,8 +2749,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2455,8 +2783,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2487,8 +2821,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2519,8 +2859,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2551,40 +2897,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37274200</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>34493200</v>
       </c>
-      <c r="E72" s="3">
-        <v>34462400</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>31150800</v>
       </c>
-      <c r="G72" s="3">
-        <v>35260500</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>33673000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>31308200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>30490200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>31371200</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2615,8 +2973,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2647,8 +3011,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2679,40 +3049,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>67169700</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3">
         <v>62415400</v>
       </c>
-      <c r="E76" s="3">
-        <v>64434500</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>59478200</v>
       </c>
-      <c r="G76" s="3">
-        <v>64709200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3">
         <v>64373800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>59366000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>59299100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>61679700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>58154300</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2743,45 +3125,57 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2812,8 +3206,14 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2826,8 +3226,10 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2858,8 +3260,14 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2890,8 +3298,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2922,8 +3336,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2954,8 +3374,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2986,8 +3412,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3018,8 +3450,14 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3050,8 +3488,14 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3064,8 +3508,10 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3096,8 +3542,14 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3128,8 +3580,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3160,8 +3618,14 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3192,8 +3656,14 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3206,8 +3676,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3238,8 +3710,14 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3270,8 +3748,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3302,8 +3786,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3334,8 +3824,14 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3366,8 +3862,14 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3398,8 +3900,14 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3428,6 +3936,12 @@
         <v>4</v>
       </c>
       <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ALIZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
   <si>
     <t>ALIZY</t>
   </si>
@@ -656,67 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -753,8 +756,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -791,8 +797,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -829,8 +838,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -845,8 +857,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -883,8 +896,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -921,8 +937,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -959,8 +978,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -997,8 +1019,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1010,8 +1035,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1048,8 +1074,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1086,8 +1115,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1102,8 +1134,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1140,8 +1173,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1178,8 +1214,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1216,8 +1255,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1254,8 +1296,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1292,8 +1337,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1330,8 +1378,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1368,8 +1419,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1406,8 +1460,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1444,8 +1501,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1482,8 +1542,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1520,8 +1583,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1558,8 +1624,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1596,8 +1665,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1634,8 +1706,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1672,8 +1747,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1710,51 +1788,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1769,8 +1853,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1785,122 +1870,132 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22846100</v>
+      </c>
+      <c r="E41" s="3">
         <v>39795700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22605900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>30063200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20913000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27960700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18939800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23114200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25551400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27960700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26655800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18939800</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>130837100</v>
+      </c>
+      <c r="E42" s="3">
         <v>115418700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>112638000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>104819500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>106995700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>90836200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>86247700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8808300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>90836200</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>86247700</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15052200</v>
+      </c>
+      <c r="E43" s="3">
         <v>16662400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13350200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15825600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14954100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14693200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13139900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>25766300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>175700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14693200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>385700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13139900</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1937,198 +2032,216 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>63385000</v>
+      </c>
+      <c r="E45" s="3">
         <v>55913100</v>
       </c>
-      <c r="E45" s="3">
-        <v>80983500</v>
-      </c>
       <c r="F45" s="3">
+        <v>80984600</v>
+      </c>
+      <c r="G45" s="3">
         <v>47159500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45268000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45360300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40840000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>85328200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26119800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45360300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27195800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40840000</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>235572400</v>
+      </c>
+      <c r="E46" s="3">
         <v>229107500</v>
       </c>
-      <c r="E46" s="3">
-        <v>233389600</v>
-      </c>
       <c r="F46" s="3">
+        <v>233390600</v>
+      </c>
+      <c r="G46" s="3">
         <v>197867800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191933200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>180161600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>162741300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>144314200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>51847000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>180161600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>54237300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>162741300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>624333700</v>
+      </c>
+      <c r="E47" s="3">
         <v>608482700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>551799400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>551094000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>570507400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>551375500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>539297900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>583580400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>733580700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>551375500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>764370900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>539297900</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7795000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7421000</v>
       </c>
-      <c r="E48" s="3">
-        <v>6789500</v>
-      </c>
       <c r="F48" s="3">
+        <v>6787500</v>
+      </c>
+      <c r="G48" s="3">
         <v>7192800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7431200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7437800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11064400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6501100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
         <v>7437800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>11064400</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26406000</v>
+      </c>
+      <c r="E49" s="3">
         <v>25903700</v>
       </c>
-      <c r="E49" s="3">
-        <v>23647400</v>
-      </c>
       <c r="F49" s="3">
+        <v>23648400</v>
+      </c>
+      <c r="G49" s="3">
         <v>24098400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24474400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>24162700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19709300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57967800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19753400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>24162700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20309600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19709300</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2165,8 +2278,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2203,46 +2319,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>220192600</v>
+      </c>
+      <c r="E52" s="3">
         <v>205978900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>182559300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>204814100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>203300500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>196905000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>185163000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>173795700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>186259500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>196905000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>194128600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>185163000</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2279,46 +2401,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1202625300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1166041100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1081455600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1069703200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1086740400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1045554600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1000210500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1097605100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>997746600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1045554600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1039247100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1000210500</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2333,8 +2461,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2349,236 +2478,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>112349400</v>
+      </c>
+      <c r="E57" s="3">
         <v>110378200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>97721300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>96351700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>97379200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1117900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>89006100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35502800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>286800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1117900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>384600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3518800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1448000</v>
       </c>
-      <c r="E58" s="3">
-        <v>2442300</v>
-      </c>
       <c r="F58" s="3">
+        <v>1949500</v>
+      </c>
+      <c r="G58" s="3">
         <v>1169000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1728700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1149600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1598800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14994800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1149600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>1200200</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24546200</v>
+      </c>
+      <c r="E59" s="3">
         <v>20689400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52414300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22747200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18754300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16325300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13709500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>61788600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>57094600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16325300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>57856400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11474800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>149273200</v>
+      </c>
+      <c r="E60" s="3">
         <v>140779800</v>
       </c>
-      <c r="E60" s="3">
-        <v>159712200</v>
-      </c>
       <c r="F60" s="3">
+        <v>159219400</v>
+      </c>
+      <c r="G60" s="3">
         <v>128141000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>124890000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25042600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>110738500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>121990400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57381500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25042600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>58241000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19373700</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>37898300</v>
+      </c>
+      <c r="E61" s="3">
         <v>41866100</v>
       </c>
-      <c r="E61" s="3">
-        <v>33625600</v>
-      </c>
       <c r="F61" s="3">
+        <v>34119500</v>
+      </c>
+      <c r="G61" s="3">
         <v>32788000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>34430200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>32381000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>32854500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28065000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>32381000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>33253200</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>924846800</v>
+      </c>
+      <c r="E62" s="3">
         <v>899492700</v>
       </c>
-      <c r="E62" s="3">
-        <v>810133600</v>
-      </c>
       <c r="F62" s="3">
+        <v>810132500</v>
+      </c>
+      <c r="G62" s="3">
         <v>834713400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>846702800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>912053500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>782344800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>873959900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>873972300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>912053500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>912163200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>873310900</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2615,8 +2763,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2653,8 +2804,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2691,46 +2845,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1124723500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1094975900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1015117500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1006690200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1018695700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>981336200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>937439400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1034586000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>933511900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>981336200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>972554300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>937439400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2745,8 +2905,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2783,8 +2944,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2821,8 +2985,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2859,8 +3026,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2897,46 +3067,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>42553700</v>
+      </c>
+      <c r="E72" s="3">
         <v>37274200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>34493200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31150800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>33673000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30490200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31371200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>34076900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31308200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30490200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>31371200</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2973,8 +3149,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3011,8 +3190,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3049,46 +3231,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>73643300</v>
+      </c>
+      <c r="E76" s="3">
         <v>67169700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62415400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59478200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>64373800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>59299100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>58154300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58950400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59366000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59299100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>61679700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58154300</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3125,51 +3313,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3206,8 +3400,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3222,8 +3419,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3260,8 +3458,11 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3298,8 +3499,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3336,8 +3540,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3374,8 +3581,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3412,8 +3622,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3450,8 +3663,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3488,8 +3704,11 @@
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3504,8 +3723,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3542,8 +3762,11 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3580,8 +3803,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3618,8 +3844,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3656,8 +3885,11 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3672,8 +3904,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3710,8 +3943,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3748,8 +3984,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3786,8 +4025,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3824,8 +4066,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3862,8 +4107,11 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3900,8 +4148,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3936,6 +4187,9 @@
         <v>4</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
